--- a/proposal/chuangzhihui-30-events-activity-only-rev.xlsx
+++ b/proposal/chuangzhihui-30-events-activity-only-rev.xlsx
@@ -8,8 +8,11 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01-活动概况" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02-主体分工收费付款" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03-往期案例" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02-定义核资源导入" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03-双会资源摘要" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04-主体分工收费付款" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05-往期案例" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06-层次叠加说明" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -458,7 +461,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L31"/>
+  <dimension ref="A1:M31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -467,12 +470,13 @@
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="28" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
-    <col width="36" customWidth="1" min="10" max="10"/>
-    <col width="28" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="36" customWidth="1" min="11" max="11"/>
     <col width="28" customWidth="1" min="12" max="12"/>
+    <col width="28" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -513,25 +517,30 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>节奏</t>
+          <t>层次</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>资源源</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>价值落点</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>行程</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>嘉宾</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>交付</t>
         </is>
@@ -575,25 +584,30 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>T-14物料→T-7邀约→T-1彩排→D日→建群回访</t>
+          <t>L0点火</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
+          <t>园区自建</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
           <t>中介渠道带看与项目推介</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>项目介绍→空间导览→政策要点→一对一洽谈→建群</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr">
         <is>
           <t>房产/产业中介、渠道机构、园区招商同事</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>方案+议程+签到+意向表+建群+回访摘要+复盘</t>
         </is>
@@ -637,25 +651,30 @@
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>同上</t>
+          <t>L0点火</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
+          <t>园区自建+投研交叉</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
           <t>金融资源链接与企业客户导入</t>
         </is>
       </c>
-      <c r="J3" s="3" t="inlineStr">
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>项目路演→金融产品对接→企业需求座谈→看场→建群</t>
         </is>
       </c>
-      <c r="K3" s="3" t="inlineStr">
+      <c r="L3" s="3" t="inlineStr">
         <is>
           <t>五大行及合作金融机构对公/科创条线</t>
         </is>
       </c>
-      <c r="L3" s="3" t="inlineStr">
+      <c r="M3" s="3" t="inlineStr">
         <is>
           <t>同上</t>
         </is>
@@ -699,25 +718,30 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>同上</t>
+          <t>L0点火</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
+          <t>园区自建</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>投研视角放大项目影响力</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>项目定位→产业赛道研判→圆桌→看场→建群</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>券商研究所、产业研究院、智库分析师</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>同上</t>
         </is>
@@ -761,25 +785,30 @@
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>同上</t>
+          <t>L0点火</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
+          <t>云创基地+科企联/服中心</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
           <t>政策与载体协同落地</t>
         </is>
       </c>
-      <c r="J5" s="3" t="inlineStr">
+      <c r="K5" s="3" t="inlineStr">
         <is>
           <t>载体介绍→政策协同→云创基地资源→看场→建群</t>
         </is>
       </c>
-      <c r="K5" s="3" t="inlineStr">
+      <c r="L5" s="3" t="inlineStr">
         <is>
           <t>区相关部门、载体代表、云创基地、服中心</t>
         </is>
       </c>
-      <c r="L5" s="3" t="inlineStr">
+      <c r="M5" s="3" t="inlineStr">
         <is>
           <t>同上</t>
         </is>
@@ -823,25 +852,30 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>同上</t>
+          <t>L1双会承接</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
+          <t>WAIC总表</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>衔接WAIC议题与园区看场</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>WAIC议题速递→园区承接→双展台→洽谈→建群</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>AI/内容企业、媒体、云创基地代表</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>同上+通稿</t>
         </is>
@@ -885,25 +919,30 @@
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>同上</t>
+          <t>L2·3F能力</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
+          <t>WAIC·大模型/Agent</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
           <t>Agent初创落位</t>
         </is>
       </c>
-      <c r="J7" s="3" t="inlineStr">
+      <c r="K7" s="3" t="inlineStr">
         <is>
           <t>签到→工作流→实操→Demo→看场</t>
         </is>
       </c>
-      <c r="K7" s="3" t="inlineStr">
+      <c r="L7" s="3" t="inlineStr">
         <is>
           <t>Agent工程师、初创团队</t>
         </is>
       </c>
-      <c r="L7" s="3" t="inlineStr">
+      <c r="M7" s="3" t="inlineStr">
         <is>
           <t>同上</t>
         </is>
@@ -947,25 +986,30 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>同上</t>
+          <t>L2·5F内容</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
+          <t>CJ·游戏风云/IP</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>ChinaJoy赛道企业/IP方入驻与展位</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>ChinaJoy赛道解读→IP授权→一对一撮合→看场→建群</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>游戏/动漫/潮玩IP方、渠道、内容公司</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>同上</t>
         </is>
@@ -1009,25 +1053,30 @@
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>立项后单独排期</t>
+          <t>另计价</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
+          <t>CJ·国际展团（另案）</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
           <t>出海需求企业服务（不在年度活动包费用内）</t>
         </is>
       </c>
-      <c r="J9" s="3" t="inlineStr">
+      <c r="K9" s="3" t="inlineStr">
         <is>
           <t>另案确定</t>
         </is>
       </c>
-      <c r="K9" s="3" t="inlineStr">
+      <c r="L9" s="3" t="inlineStr">
         <is>
           <t>另案确定</t>
         </is>
       </c>
-      <c r="L9" s="3" t="inlineStr">
+      <c r="M9" s="3" t="inlineStr">
         <is>
           <t>另案合同与交付清单</t>
         </is>
@@ -1071,25 +1120,30 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>同上</t>
+          <t>L2·3F能力</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
+          <t>WAIC·多模态/AIGC</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>多模态团队入驻</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>案例→实操→共创→评审→看场</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>多模态应用团队、产品负责人</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>同上</t>
         </is>
@@ -1133,25 +1187,30 @@
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>同上</t>
+          <t>L2·5F内容</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
+          <t>CJ·游戏风云</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
           <t>ChinaJoy生态企业集中看场与洽谈</t>
         </is>
       </c>
-      <c r="J11" s="3" t="inlineStr">
+      <c r="K11" s="3" t="inlineStr">
         <is>
           <t>开幕→赛道分享→展洽→看场→建群</t>
         </is>
       </c>
-      <c r="K11" s="3" t="inlineStr">
+      <c r="L11" s="3" t="inlineStr">
         <is>
           <t>数字娱乐企业、内容工作室、渠道</t>
         </is>
       </c>
-      <c r="L11" s="3" t="inlineStr">
+      <c r="M11" s="3" t="inlineStr">
         <is>
           <t>同上</t>
         </is>
@@ -1195,25 +1254,30 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>同上</t>
+          <t>L2·3F能力</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
+          <t>WAIC·治理标准论坛</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>合规型企业信任导入</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>治理框架→合规清单→案例→问答→对接</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>合规顾问、企业法务/负责人</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>同上</t>
         </is>
@@ -1257,25 +1321,30 @@
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>同上</t>
+          <t>L2·3F能力</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
+          <t>WAIC·算力/芯片 + CJ云服务示例</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
           <t>高算力企业定向看场</t>
         </is>
       </c>
-      <c r="J13" s="3" t="inlineStr">
+      <c r="K13" s="3" t="inlineStr">
         <is>
           <t>政策包→代金券→案例→诊断→看场</t>
         </is>
       </c>
-      <c r="K13" s="3" t="inlineStr">
+      <c r="L13" s="3" t="inlineStr">
         <is>
           <t>火山引擎、云创基地、企业技术负责人</t>
         </is>
       </c>
-      <c r="L13" s="3" t="inlineStr">
+      <c r="M13" s="3" t="inlineStr">
         <is>
           <t>同上</t>
         </is>
@@ -1319,25 +1388,30 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>同上</t>
+          <t>L2·3F能力</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
+          <t>云创+WAIC算力池</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>用券企业聚集</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>三券规则→核销→案例→开户→入驻洽谈</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>券平台、云厂商、企业负责人</t>
         </is>
       </c>
-      <c r="L14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>同上</t>
         </is>
@@ -1381,25 +1455,30 @@
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>外事流程单独排期</t>
+          <t>另计价</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
+          <t>另案</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
           <t>领事到访接待（不在三部分活动费用内）</t>
         </is>
       </c>
-      <c r="J15" s="3" t="inlineStr">
+      <c r="K15" s="3" t="inlineStr">
         <is>
           <t>另案确定</t>
         </is>
       </c>
-      <c r="K15" s="3" t="inlineStr">
+      <c r="L15" s="3" t="inlineStr">
         <is>
           <t>领事及相关方（另案）</t>
         </is>
       </c>
-      <c r="L15" s="3" t="inlineStr">
+      <c r="M15" s="3" t="inlineStr">
         <is>
           <t>另案报价与执行方案</t>
         </is>
@@ -1443,25 +1522,30 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>同上</t>
+          <t>L3叠加</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
+          <t>WAIC具身 + CJ Vision Future</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>具身/机器人团队看场</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>演示→讲解→场景→踩点→洽谈</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>具身团队、高校实验室</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
         <is>
           <t>同上</t>
         </is>
@@ -1505,25 +1589,30 @@
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>同上</t>
+          <t>L4收口</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
+          <t>双会精选项目</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
           <t>集中签约洽谈与媒体背书</t>
         </is>
       </c>
-      <c r="J17" s="3" t="inlineStr">
+      <c r="K17" s="3" t="inlineStr">
         <is>
           <t>开幕→精选路演→颁奖→洽谈</t>
         </is>
       </c>
-      <c r="K17" s="3" t="inlineStr">
+      <c r="L17" s="3" t="inlineStr">
         <is>
           <t>投资人、链主、媒体、精选项目</t>
         </is>
       </c>
-      <c r="L17" s="3" t="inlineStr">
+      <c r="M17" s="3" t="inlineStr">
         <is>
           <t>同上+签约台账</t>
         </is>
@@ -1567,25 +1656,30 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>同上</t>
+          <t>L2·5F内容</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
+          <t>WAIC·内容创意AIGC</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>厂牌/工作室入驻</t>
         </is>
       </c>
-      <c r="J18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>政策→制片→脚本→路演→看场</t>
         </is>
       </c>
-      <c r="K18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>导演、厂牌、平台方</t>
         </is>
       </c>
-      <c r="L18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>同上</t>
         </is>
@@ -1629,25 +1723,30 @@
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>同上</t>
+          <t>L2·3F能力</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
+          <t>WAIC·企业服务与营销</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
           <t>营销科技公司看场</t>
         </is>
       </c>
-      <c r="J19" s="3" t="inlineStr">
+      <c r="K19" s="3" t="inlineStr">
         <is>
           <t>策略→Agent→素材→复盘→转化</t>
         </is>
       </c>
-      <c r="K19" s="3" t="inlineStr">
+      <c r="L19" s="3" t="inlineStr">
         <is>
           <t>投放操盘手、产品经理</t>
         </is>
       </c>
-      <c r="L19" s="3" t="inlineStr">
+      <c r="M19" s="3" t="inlineStr">
         <is>
           <t>同上</t>
         </is>
@@ -1691,25 +1790,30 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>同上</t>
+          <t>L2·政策</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
+          <t>服中心+双会客群</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>内容/AI企业导入</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>政策→礼包→画像→诊断→看场</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
         <is>
           <t>政策宣讲、服中心、企业负责人</t>
         </is>
       </c>
-      <c r="L20" s="2" t="inlineStr">
+      <c r="M20" s="2" t="inlineStr">
         <is>
           <t>同上</t>
         </is>
@@ -1753,25 +1857,30 @@
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>同上</t>
+          <t>L2·政策</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
+          <t>服中心</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
           <t>待认定企业带政策入驻</t>
         </is>
       </c>
-      <c r="J21" s="3" t="inlineStr">
+      <c r="K21" s="3" t="inlineStr">
         <is>
           <t>条件→材料→初筛→套餐→激励</t>
         </is>
       </c>
-      <c r="K21" s="3" t="inlineStr">
+      <c r="L21" s="3" t="inlineStr">
         <is>
           <t>辅导顾问、待认定企业负责人</t>
         </is>
       </c>
-      <c r="L21" s="3" t="inlineStr">
+      <c r="M21" s="3" t="inlineStr">
         <is>
           <t>同上</t>
         </is>
@@ -1815,25 +1924,30 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>同上</t>
+          <t>L2·3F能力</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
+          <t>WAIC·青年/OPC + CJ创作者</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>获奖团队优先谈单元</t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>开题→开发→路演→礼包→看场</t>
         </is>
       </c>
-      <c r="K22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
         <is>
           <t>评委、投资人、Builders</t>
         </is>
       </c>
-      <c r="L22" s="2" t="inlineStr">
+      <c r="M22" s="2" t="inlineStr">
         <is>
           <t>同上</t>
         </is>
@@ -1877,25 +1991,30 @@
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t>同上</t>
+          <t>L2·学术</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
+          <t>学术支持+WAIC科研赛道</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
           <t>成果公司/实验室落户</t>
         </is>
       </c>
-      <c r="J23" s="3" t="inlineStr">
+      <c r="K23" s="3" t="inlineStr">
         <is>
           <t>成果路演→场景→承接→看单元→洽谈</t>
         </is>
       </c>
-      <c r="K23" s="3" t="inlineStr">
+      <c r="L23" s="3" t="inlineStr">
         <is>
           <t>复旦/同济技转、教授团队、住房政策研究中心学者（学术支持）</t>
         </is>
       </c>
-      <c r="L23" s="3" t="inlineStr">
+      <c r="M23" s="3" t="inlineStr">
         <is>
           <t>同上</t>
         </is>
@@ -1939,25 +2058,30 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>同上</t>
+          <t>L2·3F能力</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
+          <t>WAIC·大模型论坛</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>研究型/模型团队</t>
         </is>
       </c>
-      <c r="J24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>议题→圆桌→围炉→问答→看场</t>
         </is>
       </c>
-      <c r="K24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>学者、模型企业、投资人</t>
         </is>
       </c>
-      <c r="L24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>同上</t>
         </is>
@@ -2001,25 +2125,30 @@
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t>同上</t>
+          <t>L2·5F内容</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
+          <t>CJ·创作者展区</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
           <t>数字娱乐/内容品牌问询</t>
         </is>
       </c>
-      <c r="J25" s="3" t="inlineStr">
+      <c r="K25" s="3" t="inlineStr">
         <is>
           <t>揭幕→发布→快闪→专访→招商通道</t>
         </is>
       </c>
-      <c r="K25" s="3" t="inlineStr">
+      <c r="L25" s="3" t="inlineStr">
         <is>
           <t>创作者、媒体、渠道、ChinaJoy相关内容方</t>
         </is>
       </c>
-      <c r="L25" s="3" t="inlineStr">
+      <c r="M25" s="3" t="inlineStr">
         <is>
           <t>同上</t>
         </is>
@@ -2063,25 +2192,30 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>同上</t>
+          <t>L2·5F内容</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
+          <t>CJ·魔玩/谷子</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>ChinaJoy供应链/周边企业展位落位</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>赛道介绍→供需对接→展位参观→报价→建群</t>
         </is>
       </c>
-      <c r="K26" s="2" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
         <is>
           <t>游戏周边、潮玩供应链、渠道采购</t>
         </is>
       </c>
-      <c r="L26" s="2" t="inlineStr">
+      <c r="M26" s="2" t="inlineStr">
         <is>
           <t>同上</t>
         </is>
@@ -2125,25 +2259,30 @@
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t>同上</t>
+          <t>L2·3F能力</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
+          <t>WAIC·行业AI + ACT-006</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
           <t>成长型AI补位</t>
         </is>
       </c>
-      <c r="J27" s="3" t="inlineStr">
+      <c r="K27" s="3" t="inlineStr">
         <is>
           <t>政策→路演→点评→金融→看场</t>
         </is>
       </c>
-      <c r="K27" s="3" t="inlineStr">
+      <c r="L27" s="3" t="inlineStr">
         <is>
           <t>顾问、银行、基金、企业</t>
         </is>
       </c>
-      <c r="L27" s="3" t="inlineStr">
+      <c r="M27" s="3" t="inlineStr">
         <is>
           <t>同上</t>
         </is>
@@ -2187,25 +2326,30 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>同上</t>
+          <t>L2·5F内容</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
+          <t>CJ·创作者/市集形态</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>优质摊主/工作室升级固定展位</t>
         </is>
       </c>
-      <c r="J28" s="2" t="inlineStr">
+      <c r="K28" s="2" t="inlineStr">
         <is>
           <t>布展→体验→交流→转正洽谈→建群</t>
         </is>
       </c>
-      <c r="K28" s="2" t="inlineStr">
+      <c r="L28" s="2" t="inlineStr">
         <is>
           <t>内容工作室、周边品牌、达人</t>
         </is>
       </c>
-      <c r="L28" s="2" t="inlineStr">
+      <c r="M28" s="2" t="inlineStr">
         <is>
           <t>同上</t>
         </is>
@@ -2249,25 +2393,30 @@
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>同上</t>
+          <t>L2·5F内容</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
+          <t>CJ·IP/联名</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
           <t>IP联名/衍生品团队入驻</t>
         </is>
       </c>
-      <c r="J29" s="3" t="inlineStr">
+      <c r="K29" s="3" t="inlineStr">
         <is>
           <t>IP路演→联名模式→一对一→MOU→看场</t>
         </is>
       </c>
-      <c r="K29" s="3" t="inlineStr">
+      <c r="L29" s="3" t="inlineStr">
         <is>
           <t>IP方、衍生品商、渠道</t>
         </is>
       </c>
-      <c r="L29" s="3" t="inlineStr">
+      <c r="M29" s="3" t="inlineStr">
         <is>
           <t>同上</t>
         </is>
@@ -2311,25 +2460,30 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>展期预约制</t>
+          <t>L2·5F内容</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
+          <t>CJ·氛围落地</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>闭幕洽谈集中转化</t>
         </is>
       </c>
-      <c r="J30" s="2" t="inlineStr">
+      <c r="K30" s="2" t="inlineStr">
         <is>
           <t>布展→预约观展→交流→闭幕洽谈</t>
         </is>
       </c>
-      <c r="K30" s="2" t="inlineStr">
+      <c r="L30" s="2" t="inlineStr">
         <is>
           <t>联合内容方、渠道、品牌</t>
         </is>
       </c>
-      <c r="L30" s="2" t="inlineStr">
+      <c r="M30" s="2" t="inlineStr">
         <is>
           <t>同上</t>
         </is>
@@ -2373,25 +2527,30 @@
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>同上</t>
+          <t>L4收口/预热</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
+          <t>双会预热</t>
+        </is>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
           <t>旺季补位，双大会预热</t>
         </is>
       </c>
-      <c r="J31" s="3" t="inlineStr">
+      <c r="K31" s="3" t="inlineStr">
         <is>
           <t>发布→渠道→看场→年框→双会预热</t>
         </is>
       </c>
-      <c r="K31" s="3" t="inlineStr">
+      <c r="L31" s="3" t="inlineStr">
         <is>
           <t>IP方、渠道、媒体</t>
         </is>
       </c>
-      <c r="L31" s="3" t="inlineStr">
+      <c r="M31" s="3" t="inlineStr">
         <is>
           <t>同上</t>
         </is>
@@ -2408,7 +2567,1461 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:G31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="48" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>编号</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>活动名称</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>层次</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>定义核</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>资源源</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>资源导入（招商向）</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>价值落点</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="52" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>创智汇项目推广日①·中介与渠道专场</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>L0点火</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>渠道点火场：把「AI+数字内容共创港」讲清楚，导入后续带客池</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>园区自建</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>双会客群转介话术包；待租8间看场清单</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>中介渠道带看与项目推介</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="52" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>创智汇项目推广日②·五大行与金融机构专场</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>L0点火</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>金融转介场：用科创金融话术放大带客可信度</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>园区自建+投研交叉</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>WAIC金融科技论坛议题摘要；CJ BTOB专业观众画像</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>金融资源链接与企业客户导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="52" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>创智汇项目推广日③·投研机构专场</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>L0点火</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>叙事定调场：对外统一园区赛道故事</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>园区自建</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>WAIC赛道结论（大模型/具身/算力）；CJ「与AI同游」产业判断</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>投研视角放大项目影响力</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="52" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>P4</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>创智汇项目推广日④·政府部门与载体协同专场</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>L0点火</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>政策协同场：主体背书与载体资源上桌</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>云创基地+科企联/服中心</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>云创算力券/创新券口径；YOUNG立方政策包</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>政策与载体协同落地</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="52" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>E1</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>WAIC成果承接·创智汇开放交流日</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>L1双会承接</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>WAIC余热承接：把大会议题压缩为园区可看场的≤30人交流</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>WAIC总表</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>A/B线索抽样邀约；ACT-001/002/006议题切片；不堆全量963展商</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>衔接WAIC议题与园区看场</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="52" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Agent智能体搭建一日营</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>L2·3F能力</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>3F入孵核：Agent能力→OPC工位转化</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>WAIC·大模型/Agent</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>WAIC行业：AI Agent约87家池；ACT-001闭门会缩尺</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>Agent初创落位</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="52" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>ChinaJoy主题·数字娱乐与IP授权对接会</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>L2·5F内容</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>5F内容核：IP授权对接→展位/办公问询</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>CJ·游戏风云/IP</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>CJ优先：中小工作室+IP授权方；可触达263抽样，不追大厂总部</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>ChinaJoy赛道企业/IP方入驻与展位</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="52" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>F1</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>出海专题活动（另议·另计价）</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>另计价</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>另议核：出海不进年度包，另案另计价</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>CJ·国际展团（另案）</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>CJ BTOB外资线索仅作另案素材；本册不承诺外企到场</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>出海需求企业服务（不在年度活动包费用内）</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="52" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>多模态智能体工作坊</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>L2·3F能力</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>3F技术核：多模态团队看场入驻</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>WAIC·多模态/AIGC</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>WAIC AIGC图像/视频/3D子类抽样；论坛「内容创意与AIGC」切片</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>多模态团队入驻</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="52" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>E4</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>ChinaJoy主题日·数字娱乐生态交流</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>L2·5F内容</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>5F生态核：数字娱乐集中看场</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>CJ·游戏风云</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Express/独立游戏中小团队池；库洛/鹰角/散爆等仅作赛道示例非名单承诺</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>ChinaJoy生态企业集中看场与洽谈</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="52" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>AI治理与可信智能体沙龙</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>L2·3F能力</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>信任核：治理合规降低入驻决策摩擦</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>WAIC·治理标准论坛</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>WAIC治理赛道7场论坛议题摘要；合规顾问短名单</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>合规型企业信任导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="52" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>火山引擎×算力Infra实务营</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>L2·3F能力</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>算力核：云创基地×厂商联训→高算力看场</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>WAIC·算力/芯片 + CJ云服务示例</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>ACT-003缩尺；WAIC算力展商226家池抽样；云创算力资源</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>高算力企业定向看场</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="52" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>B4</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>创新券·算力券·模型券实务沙龙</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>L2·3F能力</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>券务核：用券企业聚集转化</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>云创+WAIC算力池</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>三券核销路径；WAIC算力/云厂商联系人抽样</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>用券企业聚集</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="52" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>L1</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>领事到访接待（另计价）</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>另计价</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>外事另计价核：到访≠挂牌，分开报价</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>另案</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>不占用年度30场资源池</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>领事到访接待（不在三部分活动费用内）</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="52" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>A5</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>具身智能空间交互体验日</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>L3叠加</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>双会叠加核：具身体验→3F/5F联合看场</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>WAIC具身 + CJ Vision Future</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>ACT-002缩尺；WAIC场景观察（零售/工业物流）；CJ前沿科技高优先级</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>具身/机器人团队看场</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="52" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>F4</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>创智汇AI年度Demo Day</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>L4收口</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>年中收口核：精选项目集中签约洽谈</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>双会精选项目</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>年内WAIC/CJ导入的A/B意向项目精选路演，不做全量路演</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>集中签约洽谈与媒体背书</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="52" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>AIGC微短剧制片特训</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>L2·5F内容</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>内容制片核：微短剧厂牌→5F展陈/3F办公</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>WAIC·内容创意AIGC</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>WAIC「AI赋能影视内容」论坛切片；AIGC厂牌抽样</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>厂牌/工作室入驻</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="52" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>A6</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>AI营销Agent实战营</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>L2·3F能力</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>营销科技核：投放团队看场入驻</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>WAIC·企业服务与营销</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>WAIC企业服务/营销86家池抽样；Agent应用团队</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>营销科技公司看场</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="52" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>YOUNG立方×智能伙伴政策沙龙</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>L2·政策</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>政策获客核：YOUNG立方礼包转化</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>服中心+双会客群</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>政策礼包+双会导入意向企业复邀</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>内容/AI企业导入</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="52" customHeight="1">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>高企认定冲刺（AI企业专场）</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>L2·政策</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>带政策入驻核：高企辅导绑定入驻套餐</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>服中心</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>双会AI应用类待认定企业名单抽样</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>待认定企业带政策入驻</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="52" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>A7</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>OPC超级个体黑客松（春）</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>L2·3F能力</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>OPC核：黑客松获奖→优先谈单元</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>WAIC·青年/OPC + CJ创作者</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>高校/青年Builder；CJ AGS高校团队线索抽样</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>获奖团队优先谈单元</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="52" customHeight="1">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>高校成果转化·AI for Science日</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>L2·学术</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>成果转化核：高校实验室/公司落户</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>学术支持+WAIC科研赛道</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>复旦住房政策研究中心学术支持位；WAIC前沿科研论坛切片</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>成果公司/实验室落户</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="52" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>F3</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>通往AGI季度圆桌</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>L2·3F能力</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>研究型客户核：闭门圆桌深谈看场</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>WAIC·大模型论坛</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>ACT-001闭门形态；模型公司抽样（不作全量邀约）</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>研究型/模型团队</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="52" customHeight="1">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>ChinaJoy主题·创作者内容首发①</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>L2·5F内容</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>创作者首发核：内容发布带招商通道</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>CJ·创作者展区</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>CJ创作者/社团抽样；渠道复用（抖音/小红书玩法迁移园区）</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>数字娱乐/内容品牌问询</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="52" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>ChinaJoy主题·游戏周边与潮玩供应链对接</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>L2·5F内容</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>供应链核：周边/潮玩→5F展位落位</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>CJ·魔玩/谷子</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>CJ潮玩谷子高优先级；JOYTOY/卡游等仅作品类示例</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>ChinaJoy供应链/周边企业展位落位</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="52" customHeight="1">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>专精特新·AI应用培育路演</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>L2·3F能力</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>成长补位核：专精特新AI应用看场</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>WAIC·行业AI + ACT-006</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>ACT-006案例圆桌缩尺；行业AI114家池抽样</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>成长型AI补位</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="52" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>ChinaJoy主题·数字娱乐市集体验日</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>L2·5F内容</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>市集转化核：摊主升级固定展位</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>CJ·创作者/市集形态</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>CJ创作者展区小微品牌；市集→固定展位升级路径</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>优质摊主/工作室升级固定展位</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="52" customHeight="1">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>C5</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>ChinaJoy主题·IP联名与衍生品撮合会</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>L2·5F内容</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>IP商业化核：联名撮合→入驻/展位</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>CJ·IP/联名</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>CJ老字号×IP联名案例迁移；衍生品商抽样</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>IP联名/衍生品团队入驻</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="52" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>D4</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>ChinaJoy主题·沉浸式数字娱乐联展</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>L2·5F内容</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>视觉落地核：短展期氛围→闭幕洽谈</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>CJ·氛围落地</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>联合内容方短名单；预约制控流≤30人/场</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>闭幕洽谈集中转化</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="52" customHeight="1">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>D5</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>创作者首发②·衔接WAIC2027与ChinaJoy</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>L4收口/预热</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>双会预热核：创作者首发衔接下一年双会</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>双会预热</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>全年双会导入线索复盘；预热WAIC2027+下届CJ</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>旺季补位，双大会预热</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>会展</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>指标/策略</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>招商用法</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>映射场次</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="40" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>WAIC</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>参展商963 · 品牌主库4262 · 联系人3463 · A/B线索500 · 论坛175</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>A/B线索抽样+议题缩尺，不粘贴全库</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>E1/A2/A3/A4/A5/B2/B4/C4/F3/F4</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="40" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>WAIC</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>ACT-001 大模型闭门</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>缩尺为≤30人 Agent/圆桌</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>A2/A3/F3</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="40" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>WAIC</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>ACT-002 机器人体验供需</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>体验日+看场</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>A5/E1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="40" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>WAIC</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>ACT-003 算力芯片峰会</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>厂商联训+券务</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>A4/B4</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="40" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>WAIC</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>ACT-006 行业AI案例</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>路演/政策沙龙</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>C4/B1</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="40" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>ChinaJoy</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>近900家参展 · 可触达优先263 · 精编422 · 主题与AI同游</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>可触达263优先外呼抽样</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>C1/E4/D2/C3/D3/C5/D4/D5</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="40" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>ChinaJoy</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>最高：中小游戏工作室</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Express/Next Play/AGS 孵化向</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>C1/E4/D2</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="40" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>ChinaJoy</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>高：具身 Vision Future</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>与WAIC具身叠加</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>A5/E1</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="40" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>ChinaJoy</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>高：潮玩谷子供应链</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>5F展位/市集转正</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>C3/D3/C5</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="40" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>ChinaJoy</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>中高：创作者经济</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>首发+渠道复用</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>D2/D5</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="40" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>原则</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>中腰部灵活/不追大厂总部</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>双会是资源库，30场是定义核</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>全册</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2615,7 +4228,19 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>活动同步衔接 WAIC 与 ChinaJoy</t>
+          <t>WAIC→3F能力线；ChinaJoy→5F内容线；具身/AIGC为叠加带</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="34" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>资源原则</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>双会总表只取招商贴近切片；不做全量名单堆砌</t>
         </is>
       </c>
     </row>
@@ -2624,7 +4249,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2756,4 +4381,178 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>层次</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>作用</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>主要来源</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>对应场次</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="36" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>L0 点火</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>渠道/金融/投研/政府点火</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>园区自建+载体</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>P1–P4</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="36" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>L1 双会承接</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>大会余热→园区看场</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>WAIC成果切片</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>E1</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>L2 楼层主线</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>3F能力 / 5F内容分轨</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>WAIC赛道 + CJ优先策略</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>A/B 与 C/D</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="36" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>L3 双会叠加带</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>具身+AIGC跨楼层</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>WAIC具身×CJ Vision Future</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>A5 等</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="36" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>L4 收口/预热</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>签约收口与下届预热</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>年内导入精选</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>F4 / D5</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="36" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>另计价</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>出海/领事不进年度包</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>另案</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>F1 / L1</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/proposal/chuangzhihui-30-events-activity-only-rev.xlsx
+++ b/proposal/chuangzhihui-30-events-activity-only-rev.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -641,7 +641,7 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -909,7 +909,7 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1311,7 +1311,7 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1512,7 +1512,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1579,7 +1579,7 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1713,7 +1713,7 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
@@ -1780,7 +1780,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1981,7 +1981,7 @@
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
@@ -2182,7 +2182,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -2383,7 +2383,7 @@
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
@@ -2450,7 +2450,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -2517,7 +2517,7 @@
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>约50%</t>
+          <t>≤30%</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
@@ -4120,7 +4120,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>适度承兑约50%，不做100%承诺</t>
+          <t>≤30%</t>
         </is>
       </c>
     </row>
